--- a/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:53</t>
+          <t>2026-10-06 01:23:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:54</t>
+          <t>2026-10-06 01:23:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:56</t>
+          <t>2026-10-06 01:23:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:57</t>
+          <t>2026-10-06 01:23:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:57</t>
+          <t>2026-10-06 01:23:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:57</t>
+          <t>2026-10-06 01:23:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:57</t>
+          <t>2026-10-06 01:23:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:57</t>
+          <t>2026-10-06 01:23:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:46</t>
+          <t>2026-10-06 02:27:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:48</t>
+          <t>2026-10-06 02:27:24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:49</t>
+          <t>2026-10-06 02:27:25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:50</t>
+          <t>2026-10-06 02:27:27</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.31%753,000</t>
+          <t>9.26%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.31%</t>
+          <t>9.26%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5165</v>
+        <v>4920</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.10%249,000</t>
+          <t>6.14%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.10%</t>
+          <t>6.14%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+9.96%13355</t>
+          <t>-1.91%13100</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>13355</v>
+        <v>13100</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.75%79,000</t>
+          <t>5.04%79,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5700</v>
+        <v>5995</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.26%166,000</t>
+          <t>4.52%166,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.52%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1325</v>
+        <v>1310</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.04%625,000</t>
+          <t>3.95%625,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>3.95%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2005</v>
+        <v>2050</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.77%404,000</t>
+          <t>3.87%404,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>-1.73%7080</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7205</v>
+        <v>7080</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.50%104,000</t>
+          <t>3.58%104,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+10%286</t>
+          <t>+2.45%293</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.11%2,416,000</t>
+          <t>3.30%2,416,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.76%530</t>
+          <t>+1.55%5905</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>530</v>
+        <v>5905</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.85%1,096,000</t>
+          <t>2.86%103,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1096000</v>
+        <v>103000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+4.21%5815</t>
+          <t>-0.94%525</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5815</v>
+        <v>525</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.84%103,000</t>
+          <t>2.77%1,096,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>103000</v>
+        <v>1096000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.56%3000</t>
+          <t>-2.62%8375</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3000</v>
+        <v>8375</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.34%161,600</t>
+          <t>2.42%59,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>161600</v>
+        <v>59000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+8.86%8600</t>
+          <t>-2.67%2920</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+8.86%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8600</v>
+        <v>2920</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.31%59,000</t>
+          <t>2.32%161,600</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>59000</v>
+        <v>161600</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.28%134,000</t>
+          <t>2.29%134,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>+0.27%744</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.19%621,000</t>
+          <t>2.20%621,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:23</t>
+          <t>2026-10-06 23:19:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+1.12%181</t>
+          <t>-1.93%177.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>181</v>
+        <v>177.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.03%2,293,000</t>
+          <t>1.98%2,293,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.2%254</t>
+          <t>+0.79%256</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.01%1,616,000</t>
+          <t>1.96%1,616,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>+3.7%1260</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5520</v>
+        <v>1260</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.94%74,000</t>
+          <t>1.96%337,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>74000</v>
+        <v>337000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+3.61%19520</t>
+          <t>+2.72%5670</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>19520</v>
+        <v>5670</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.89%20,300</t>
+          <t>1.95%74,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>20300</v>
+        <v>74000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+9.95%1215</t>
+          <t>-2.74%18985</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+9.95%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1215</v>
+        <v>18985</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.84%337,000</t>
+          <t>1.89%20,300</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>337000</v>
+        <v>20300</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.22%6205</t>
+          <t>-1.21%6130</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6205</v>
+        <v>6130</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.83%61,000</t>
+          <t>1.81%61,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>+0.67%1505</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.81%251,000</t>
+          <t>1.79%251,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.24%2100</t>
+          <t>-0.48%2090</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.74%168,000</t>
+          <t>1.68%168,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2150</v>
+        <v>2350</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.60%155,105</t>
+          <t>1.64%148,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>155105</v>
+        <v>148000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,34 +1907,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2325</v>
+        <v>2290</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.60%148,000</t>
+          <t>1.59%155,105</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>148000</v>
+        <v>155105</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%626</t>
+          <t>-0.16%625</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.50%485,000</t>
+          <t>1.45%485,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.38%142,000</t>
+          <t>1.41%142,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+4.29%1095</t>
+          <t>-2.28%1070</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1095</v>
+        <v>1070</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.38%266,000</t>
+          <t>1.39%266,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.16%817</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>817</v>
+        <v>6855</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.18%286,000</t>
+          <t>1.22%38,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>286000</v>
+        <v>38000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>-1.4%1755</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6730</v>
+        <v>1755</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.18%38,000</t>
+          <t>1.22%143,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>38000</v>
+        <v>143000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:24</t>
+          <t>2026-10-06 23:19:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>+0.76%333.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>152.5</v>
+        <v>333.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.18%1,474,000</t>
+          <t>1.13%718,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1474000</v>
+        <v>718000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.3%331</t>
+          <t>-2.57%796</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>331</v>
+        <v>796</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.18%718,000</t>
+          <t>1.12%286,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>718000</v>
+        <v>286000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+9.88%1780</t>
+          <t>-3.28%147.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1780</v>
+        <v>147.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.15%143,000</t>
+          <t>1.07%1,474,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>143000</v>
+        <v>1474000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0%213.5</t>
+          <t>+0.7%215</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>213.5</v>
+        <v>215</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.96%906,000</t>
+          <t>0.92%906,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.15%67.4</t>
+          <t>+1.48%68.4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>67.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.93%2,781,000</t>
+          <t>0.90%2,781,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+4.02%388.5</t>
+          <t>-2.19%380</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+4.02%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>388.5</v>
+        <v>380</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.89%484,000</t>
+          <t>0.90%484,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.61%189.5</t>
+          <t>+4.79%787</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>+4.79%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>189.5</v>
+        <v>787</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.87%948,000</t>
+          <t>0.90%252,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>948000</v>
+        <v>252000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+9.96%751</t>
+          <t>0%189.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>751</v>
+        <v>189.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.85%252,000</t>
+          <t>0.86%948,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>252000</v>
+        <v>948000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.38%794</t>
+          <t>-1.76%780</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-1.76%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.80%204,000</t>
+          <t>0.77%204,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.43%241.5</t>
+          <t>+1.86%246</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>241.5</v>
+        <v>246</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.79%650,000</t>
+          <t>0.75%650,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.58%68.8</t>
+          <t>-0.15%68.7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.76%2,255,500</t>
+          <t>0.74%2,255,500</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.94%1605</t>
+          <t>-0.93%1590</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1605</v>
+        <v>1590</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.72%91,000</t>
+          <t>0.70%91,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.47%3155</t>
+          <t>-1.27%3115</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.47%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3155</v>
+        <v>3115</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.69%44,000</t>
+          <t>0.66%44,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.21%44.8</t>
+          <t>+1.45%45.45</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>44.8</v>
+        <v>45.45</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.66%2,962,622</t>
+          <t>0.63%2,962,622</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+6.06%2450</t>
+          <t>-1.43%2415</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+6.06%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2450</v>
+        <v>2415</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.62%54,000</t>
+          <t>0.63%54,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:25</t>
+          <t>2026-10-06 23:19:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>-6.44%2325</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2485</v>
+        <v>2325</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.61%48,336</t>
+          <t>0.57%48,336</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:27</t>
+          <t>2026-10-06 23:19:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.77%557</t>
+          <t>+3.95%579</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.77%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:27</t>
+          <t>2026-10-06 23:19:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6831邁科</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.66%489</t>
+          <t>+0.31%1600</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.66%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>489</v>
+        <v>1600</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.43%182,000</t>
+          <t>0.44%58,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>182000</v>
+        <v>58000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:27</t>
+          <t>2026-10-06 23:19:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6831邁科</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+5.63%1595</t>
+          <t>+1.74%497.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+5.63%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1595</v>
+        <v>497.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.43%58,000</t>
+          <t>0.42%182,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>58000</v>
+        <v>182000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:27</t>
+          <t>2026-10-06 23:19:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+5.83%890</t>
+          <t>-0.56%885</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+5.83%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:27</t>
+          <t>2026-10-06 23:19:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+4.92%1705</t>
+          <t>-3.23%1650</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+4.92%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1705</v>
+        <v>1650</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:03</t>
+          <t>2026-10-06 23:27:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:04</t>
+          <t>2026-10-06 23:27:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:05</t>
+          <t>2026-10-06 23:27:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:06</t>
+          <t>2026-10-06 23:27:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:06</t>
+          <t>2026-10-06 23:27:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:06</t>
+          <t>2026-10-06 23:27:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:06</t>
+          <t>2026-10-06 23:27:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:06</t>
+          <t>2026-10-06 23:27:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:33</t>
+          <t>2026-10-06 23:58:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:34</t>
+          <t>2026-10-06 23:58:06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:35</t>
+          <t>2026-10-06 23:58:08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:36</t>
+          <t>2026-10-06 23:58:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
